--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:26:54+00:00</t>
+    <t>2025-01-23T13:26:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T13:26:37+00:00</t>
+    <t>2025-01-24T17:22:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T17:22:23+00:00</t>
+    <t>2025-01-29T14:25:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T14:25:50+00:00</t>
+    <t>2025-01-29T15:50:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T15:50:40+00:00</t>
+    <t>2025-01-30T15:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T15:03:39+00:00</t>
+    <t>2025-01-31T08:45:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$80</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1855" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3003" uniqueCount="482">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T08:45:39+00:00</t>
+    <t>2025-02-18T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -332,13 +332,203 @@
 </t>
   </si>
   <si>
-    <t>Composition.implicitRules</t>
+    <t>Composition.meta.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Composition.meta.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Composition.meta.versionId</t>
+  </si>
+  <si>
+    <t>Version specific identifier</t>
+  </si>
+  <si>
+    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+  </si>
+  <si>
+    <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t>Composition.meta.lastUpdated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>When the resource version last changed</t>
+  </si>
+  <si>
+    <t>When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4/http.html#read) interaction.</t>
+  </si>
+  <si>
+    <t>Meta.lastUpdated</t>
+  </si>
+  <si>
+    <t>Composition.meta.source</t>
   </si>
   <si>
     <t xml:space="preserve">uri
 </t>
   </si>
   <si>
+    <t>Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
+  </si>
+  <si>
+    <t>Meta.source</t>
+  </si>
+  <si>
+    <t>Composition.meta.profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(StructureDefinition)
+</t>
+  </si>
+  <si>
+    <t>Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
+    <t>Modèle du document et version du modèle</t>
+  </si>
+  <si>
+    <t>Meta.profile</t>
+  </si>
+  <si>
+    <t>Composition.meta.profile:canonical</t>
+  </si>
+  <si>
+    <t>canonical</t>
+  </si>
+  <si>
+    <t>Composition.meta.security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+  </si>
+  <si>
+    <t>Meta.security</t>
+  </si>
+  <si>
+    <t>Composition.meta.tag</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+  </si>
+  <si>
+    <t>Meta.tag</t>
+  </si>
+  <si>
+    <t>Composition.implicitRules</t>
+  </si>
+  <si>
     <t>A set of rules under which this content was created</t>
   </si>
   <si>
@@ -434,28 +624,13 @@
     <t>Composition.extension</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
     <t>Extension</t>
   </si>
   <si>
     <t>An Extension</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Composition.extension:versionNumber</t>
@@ -481,11 +656,23 @@
 </t>
   </si>
   <si>
+    <t>Composition.extension:data-enterer</t>
+  </si>
+  <si>
+    <t>data-enterer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-data-enterer-extension}
+</t>
+  </si>
+  <si>
+    <t>Opérateur de saisie</t>
+  </si>
+  <si>
+    <t>Extension permettant d'ajouter un opérateur de saisie dans la Composition.</t>
+  </si>
+  <si>
     <t>Composition.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
   </si>
   <si>
     <t>Extensions that cannot be ignored</t>
@@ -495,9 +682,6 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -566,9 +750,6 @@
     <t>interim: .completionCode="IN" &amp; ./statusCode[isNormalDatatype()]="active";  final: .completionCode="AU" &amp;&amp;  ./statusCode[isNormalDatatype()]="complete" and not(./inboundRelationship[typeCode="SUBJ" and isNormalActRelationship()]/source[subsumesCode("ActClass#CACT") and moodCode="EVN" and domainMember("ReviseComposition", code) and isNormalAct()]);  amended: .completionCode="AU" &amp;&amp;  ./statusCode[isNormalDatatype()]="complete" and ./inboundRelationship[typeCode="SUBJ" and isNormalActRelationship()]/source[subsumesCode("ActClass#CACT") and moodCode="EVN" and domainMember("ReviseComposition", code) and isNormalAct() and statusCode="completed"];  withdrawn : .completionCode=NI &amp;&amp;  ./statusCode[isNormalDatatype()]="obsolete"</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>DocumentReference.status</t>
   </si>
   <si>
@@ -630,9 +811,6 @@
     <t>Helps humans to assess whether the composition is of interest when viewing an index of compositions or documents.</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
     <t>High-level kind of a clinical document at a macro level.</t>
   </si>
   <si>
@@ -682,32 +860,7 @@
     <t>Composition.subject.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>Composition.subject.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Composition.subject.reference</t>
@@ -740,9 +893,6 @@
   </si>
   <si>
     <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>extensible</t>
   </si>
   <si>
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
@@ -858,7 +1008,7 @@
     <t>Composition.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Device|Patient|RelatedPerson|Organization)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-fhir-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-device-document)
 </t>
   </si>
   <si>
@@ -886,6 +1036,40 @@
     <t>FiveWs.author</t>
   </si>
   <si>
+    <t>Composition.author.id</t>
+  </si>
+  <si>
+    <t>Composition.author.extension</t>
+  </si>
+  <si>
+    <t>Composition.author.extension:time</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-author-time}
+</t>
+  </si>
+  <si>
+    <t>Horodatage de la participation de l’auteur.</t>
+  </si>
+  <si>
+    <t>Extension permettant d'ajouter un horodatage (TS) à l'élément author d'une Composition.</t>
+  </si>
+  <si>
+    <t>Composition.author.reference</t>
+  </si>
+  <si>
+    <t>Composition.author.type</t>
+  </si>
+  <si>
+    <t>Composition.author.identifier</t>
+  </si>
+  <si>
+    <t>Composition.author.display</t>
+  </si>
+  <si>
     <t>Composition.title</t>
   </si>
   <si>
@@ -932,6 +1116,9 @@
   </si>
   <si>
     <t>Composition.attester</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t xml:space="preserve">BackboneElement
@@ -950,6 +1137,10 @@
     <t>Identifies responsibility for the accuracy of the composition content.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:mode}
+</t>
+  </si>
+  <si>
     <t>.participation[typeCode="AUTHEN"].role[classCode="ASSIGNED"]</t>
   </si>
   <si>
@@ -1047,6 +1238,64 @@
   </si>
   <si>
     <t>FiveWs.witness</t>
+  </si>
+  <si>
+    <t>Composition.attester:legal</t>
+  </si>
+  <si>
+    <t>legal</t>
+  </si>
+  <si>
+    <t>Responsable du document</t>
+  </si>
+  <si>
+    <t>Composition.attester:legal.id</t>
+  </si>
+  <si>
+    <t>Composition.attester:legal.extension</t>
+  </si>
+  <si>
+    <t>Composition.attester:legal.modifierExtension</t>
+  </si>
+  <si>
+    <t>Composition.attester:legal.mode</t>
+  </si>
+  <si>
+    <t>Composition.attester:legal.time</t>
+  </si>
+  <si>
+    <t>Composition.attester:legal.party</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document)
+</t>
+  </si>
+  <si>
+    <t>Composition.attester:professional</t>
+  </si>
+  <si>
+    <t>professional</t>
+  </si>
+  <si>
+    <t>Professionnel attestant la validité du contenu du document</t>
+  </si>
+  <si>
+    <t>Composition.attester:professional.id</t>
+  </si>
+  <si>
+    <t>Composition.attester:professional.extension</t>
+  </si>
+  <si>
+    <t>Composition.attester:professional.modifierExtension</t>
+  </si>
+  <si>
+    <t>Composition.attester:professional.mode</t>
+  </si>
+  <si>
+    <t>Composition.attester:professional.time</t>
+  </si>
+  <si>
+    <t>Composition.attester:professional.party</t>
   </si>
   <si>
     <t>Composition.custodian</t>
@@ -1579,10 +1828,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO49"/>
+  <dimension ref="A1:AO80"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="38.8359375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.2890625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.8359375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="15.125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -1592,7 +1841,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="109.8125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1606,7 +1855,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="65.28515625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="73.84765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -2120,10 +2369,10 @@
         <v>77</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="K5" t="s" s="2">
         <v>104</v>
@@ -2134,9 +2383,7 @@
       <c r="M5" t="s" s="2">
         <v>106</v>
       </c>
-      <c r="N5" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>77</v>
@@ -2185,25 +2432,25 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG5" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH5" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK5" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL5" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="AG5" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH5" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI5" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ5" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK5" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL5" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>77</v>
@@ -2224,14 +2471,14 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -2243,16 +2490,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2278,49 +2525,49 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="Y6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA6" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB6" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="Z6" t="s" s="2">
+      <c r="AC6" t="s" s="2">
         <v>116</v>
       </c>
-      <c r="AA6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB6" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC6" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AD6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>77</v>
@@ -2334,14 +2581,14 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2357,10 +2604,10 @@
         <v>77</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>121</v>
@@ -2437,7 +2684,7 @@
         <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -2451,21 +2698,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>77</v>
@@ -2474,19 +2721,19 @@
         <v>77</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2536,25 +2783,25 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>77</v>
@@ -2568,10 +2815,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2582,7 +2829,7 @@
         <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>77</v>
@@ -2591,18 +2838,20 @@
         <v>77</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="N9" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>77</v>
@@ -2639,29 +2888,31 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>139</v>
+        <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2681,20 +2932,18 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="C10" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>79</v>
@@ -2706,19 +2955,19 @@
         <v>77</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2756,19 +3005,19 @@
         <v>77</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>77</v>
+        <v>143</v>
       </c>
       <c r="AD10" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2777,10 +3026,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>148</v>
+        <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2800,46 +3049,46 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="D11" t="s" s="2">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J11" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="J11" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K11" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O11" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>77</v>
       </c>
@@ -2848,7 +3097,7 @@
         <v>77</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>77</v>
@@ -2887,7 +3136,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2899,13 +3148,13 @@
         <v>77</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2919,10 +3168,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2933,10 +3182,10 @@
         <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>77</v>
@@ -2945,16 +3194,16 @@
         <v>91</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2980,13 +3229,13 @@
         <v>77</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>77</v>
@@ -3004,13 +3253,13 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>77</v>
@@ -3019,27 +3268,27 @@
         <v>102</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>161</v>
+        <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>162</v>
+        <v>77</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>163</v>
+        <v>77</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3047,35 +3296,33 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>170</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>77</v>
       </c>
@@ -3099,13 +3346,13 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>77</v>
@@ -3123,13 +3370,13 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>77</v>
@@ -3138,27 +3385,27 @@
         <v>102</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>174</v>
+        <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>175</v>
+        <v>77</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>177</v>
+        <v>77</v>
       </c>
       <c r="AO13" t="s" s="2">
-        <v>178</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3166,35 +3413,33 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I14" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="I14" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="J14" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>180</v>
+        <v>132</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>184</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>77</v>
       </c>
@@ -3218,13 +3463,13 @@
         <v>77</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>185</v>
+        <v>77</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>186</v>
+        <v>77</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>77</v>
@@ -3242,10 +3487,10 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>90</v>
@@ -3257,27 +3502,27 @@
         <v>102</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>187</v>
+        <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>188</v>
+        <v>77</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>190</v>
+        <v>77</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>191</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>192</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3288,7 +3533,7 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>77</v>
@@ -3297,23 +3542,21 @@
         <v>77</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>77</v>
       </c>
@@ -3337,13 +3580,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>198</v>
+        <v>175</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>199</v>
+        <v>176</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3361,13 +3604,13 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>77</v>
@@ -3376,63 +3619,61 @@
         <v>102</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>200</v>
+        <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>202</v>
+        <v>77</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>191</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>77</v>
+        <v>179</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
       </c>
@@ -3480,7 +3721,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3498,35 +3739,35 @@
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>210</v>
+        <v>77</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>212</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>213</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>213</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>77</v>
+        <v>187</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>77</v>
@@ -3538,15 +3779,17 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>191</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3595,13 +3838,13 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>77</v>
@@ -3613,7 +3856,7 @@
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3627,18 +3870,18 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>79</v>
@@ -3653,17 +3896,15 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3700,19 +3941,17 @@
         <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="AC18" s="2"/>
       <c r="AD18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3724,13 +3963,13 @@
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3744,42 +3983,44 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="C19" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="D19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>225</v>
+        <v>202</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3829,25 +4070,25 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>227</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3861,18 +4102,20 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="D20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>90</v>
@@ -3884,20 +4127,18 @@
         <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>104</v>
+        <v>207</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>232</v>
-      </c>
+        <v>209</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3922,13 +4163,13 @@
         <v>77</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>233</v>
+        <v>77</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>234</v>
+        <v>77</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>235</v>
+        <v>77</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>77</v>
@@ -3946,25 +4187,25 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3978,44 +4219,46 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>237</v>
+        <v>210</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>237</v>
+        <v>210</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>157</v>
+        <v>111</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>238</v>
+        <v>211</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>239</v>
+        <v>212</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
       </c>
@@ -4063,25 +4306,25 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>241</v>
+        <v>214</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>242</v>
+        <v>193</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -4095,10 +4338,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4106,13 +4349,13 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>77</v>
@@ -4121,16 +4364,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>244</v>
+        <v>217</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>245</v>
+        <v>218</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>246</v>
+        <v>219</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4180,7 +4423,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4195,27 +4438,27 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>77</v>
+        <v>220</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>133</v>
+        <v>221</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>77</v>
+        <v>222</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>77</v>
+        <v>223</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>77</v>
+        <v>224</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4223,32 +4466,34 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="J23" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>249</v>
+        <v>170</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="O23" t="s" s="2">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4273,13 +4518,13 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>77</v>
+        <v>230</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>77</v>
+        <v>231</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>77</v>
+        <v>232</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
@@ -4297,10 +4542,10 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>248</v>
+        <v>225</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>90</v>
@@ -4312,27 +4557,27 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>255</v>
+        <v>108</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>257</v>
+        <v>236</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4355,19 +4600,19 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>262</v>
+        <v>241</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4392,13 +4637,13 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>77</v>
+        <v>174</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>77</v>
+        <v>243</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>77</v>
+        <v>244</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4416,7 +4661,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>258</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>90</v>
@@ -4431,27 +4676,27 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>268</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4459,13 +4704,13 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>77</v>
@@ -4474,17 +4719,19 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>270</v>
+        <v>238</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="N25" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="O25" t="s" s="2">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4509,13 +4756,13 @@
         <v>77</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>77</v>
+        <v>255</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>77</v>
+        <v>256</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -4533,10 +4780,10 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>79</v>
@@ -4548,27 +4795,27 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>276</v>
+        <v>108</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>278</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4591,18 +4838,20 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>214</v>
+        <v>261</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
       </c>
@@ -4650,10 +4899,10 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>90</v>
@@ -4668,24 +4917,24 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>77</v>
+        <v>269</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>286</v>
+        <v>270</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4699,26 +4948,24 @@
         <v>90</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>287</v>
+        <v>105</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4743,13 +4990,13 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>290</v>
+        <v>77</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>291</v>
+        <v>77</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>77</v>
@@ -4767,7 +5014,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>286</v>
+        <v>107</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4779,19 +5026,19 @@
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>292</v>
+        <v>108</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>292</v>
+        <v>77</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>293</v>
+        <v>77</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>77</v>
@@ -4799,14 +5046,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4816,7 +5063,7 @@
         <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>77</v>
@@ -4825,20 +5072,18 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>295</v>
+        <v>111</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>296</v>
+        <v>112</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>297</v>
+        <v>113</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
@@ -4874,19 +5119,19 @@
         <v>77</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>294</v>
+        <v>118</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4898,19 +5143,19 @@
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>300</v>
+        <v>108</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>301</v>
+        <v>77</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>302</v>
+        <v>77</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>77</v>
@@ -4918,10 +5163,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>303</v>
+        <v>272</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4929,30 +5174,32 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>214</v>
+        <v>104</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>215</v>
+        <v>273</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -5001,7 +5248,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>217</v>
+        <v>276</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5010,16 +5257,16 @@
         <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>277</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -5033,21 +5280,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>304</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>304</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>77</v>
@@ -5056,19 +5303,19 @@
         <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>219</v>
+        <v>279</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>153</v>
+        <v>281</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5094,13 +5341,13 @@
         <v>77</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>77</v>
+        <v>282</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>77</v>
+        <v>283</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>77</v>
@@ -5118,25 +5365,25 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>222</v>
+        <v>284</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>176</v>
+        <v>193</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -5150,46 +5397,44 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>306</v>
+        <v>77</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>135</v>
+        <v>216</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>308</v>
+        <v>287</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>77</v>
       </c>
@@ -5237,25 +5482,25 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>133</v>
+        <v>290</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -5269,10 +5514,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5280,33 +5525,33 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J32" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J32" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K32" t="s" s="2">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5330,13 +5575,13 @@
         <v>77</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>314</v>
+        <v>77</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>315</v>
+        <v>77</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>77</v>
@@ -5354,10 +5599,10 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>90</v>
@@ -5372,10 +5617,10 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>316</v>
+        <v>193</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>317</v>
+        <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>77</v>
@@ -5386,10 +5631,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5403,26 +5648,26 @@
         <v>90</v>
       </c>
       <c r="H33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J33" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J33" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K33" t="s" s="2">
-        <v>259</v>
+        <v>297</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>319</v>
+        <v>298</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>321</v>
+        <v>300</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5471,7 +5716,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>318</v>
+        <v>296</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5486,27 +5731,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>77</v>
+        <v>301</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>322</v>
+        <v>302</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>77</v>
+        <v>304</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>77</v>
+        <v>305</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5514,7 +5759,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>90</v>
@@ -5526,20 +5771,22 @@
         <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="O34" t="s" s="2">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5588,10 +5835,10 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>90</v>
@@ -5603,27 +5850,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>77</v>
+        <v>312</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>330</v>
+        <v>314</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>77</v>
+        <v>315</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>331</v>
+        <v>316</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5631,10 +5878,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>91</v>
@@ -5646,19 +5893,17 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5707,13 +5952,13 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>77</v>
@@ -5722,27 +5967,27 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>77</v>
+        <v>322</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>77</v>
+        <v>326</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5753,7 +5998,7 @@
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>77</v>
@@ -5765,17 +6010,15 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>295</v>
+        <v>104</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>342</v>
+        <v>105</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>344</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5824,31 +6067,31 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>341</v>
+        <v>107</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>345</v>
+        <v>108</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>346</v>
+        <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>347</v>
+        <v>77</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>77</v>
@@ -5856,10 +6099,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>348</v>
+        <v>328</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>348</v>
+        <v>328</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5867,10 +6110,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>77</v>
@@ -5882,13 +6125,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>214</v>
+        <v>111</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5927,37 +6170,37 @@
         <v>77</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>217</v>
+        <v>118</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
@@ -5971,21 +6214,23 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>328</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>330</v>
+      </c>
       <c r="D38" t="s" s="2">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>77</v>
@@ -5997,17 +6242,15 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>135</v>
+        <v>331</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>219</v>
+        <v>332</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>153</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6056,7 +6299,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>222</v>
+        <v>118</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6068,13 +6311,13 @@
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -6088,46 +6331,44 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>306</v>
+        <v>77</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>307</v>
+        <v>273</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>308</v>
+        <v>274</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
       </c>
@@ -6175,25 +6416,25 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>309</v>
+        <v>276</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>77</v>
+        <v>277</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>133</v>
+        <v>193</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -6207,10 +6448,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>351</v>
+        <v>335</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6218,7 +6459,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>90</v>
@@ -6230,19 +6471,19 @@
         <v>77</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>352</v>
+        <v>279</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>353</v>
+        <v>280</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>354</v>
+        <v>281</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6268,13 +6509,13 @@
         <v>77</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>355</v>
+        <v>282</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>356</v>
+        <v>283</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>77</v>
@@ -6292,10 +6533,10 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>351</v>
+        <v>284</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>90</v>
@@ -6310,13 +6551,13 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>357</v>
+        <v>193</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>358</v>
+        <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>359</v>
+        <v>77</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>77</v>
@@ -6324,10 +6565,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>360</v>
+        <v>336</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>360</v>
+        <v>336</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6335,7 +6576,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>90</v>
@@ -6347,18 +6588,20 @@
         <v>77</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>361</v>
+        <v>216</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>362</v>
+        <v>286</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6407,10 +6650,10 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>360</v>
+        <v>289</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>90</v>
@@ -6425,13 +6668,13 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>364</v>
+        <v>290</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>365</v>
+        <v>77</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>366</v>
+        <v>77</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>77</v>
@@ -6439,10 +6682,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>367</v>
+        <v>337</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>367</v>
+        <v>337</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6453,7 +6696,7 @@
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>77</v>
@@ -6465,20 +6708,18 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>295</v>
+        <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>368</v>
+        <v>292</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>369</v>
+        <v>293</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>371</v>
-      </c>
+        <v>294</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>77</v>
       </c>
@@ -6526,13 +6767,13 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>367</v>
+        <v>295</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>77</v>
@@ -6544,13 +6785,13 @@
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>372</v>
+        <v>193</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>373</v>
+        <v>77</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>374</v>
+        <v>77</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>77</v>
@@ -6558,10 +6799,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>375</v>
+        <v>338</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>375</v>
+        <v>338</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6569,30 +6810,32 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>214</v>
+        <v>104</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>215</v>
+        <v>339</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>340</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>341</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6641,10 +6884,10 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>217</v>
+        <v>338</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>90</v>
@@ -6653,19 +6896,19 @@
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>176</v>
+        <v>342</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>77</v>
+        <v>343</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>77</v>
+        <v>344</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>77</v>
@@ -6673,42 +6916,42 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>376</v>
+        <v>345</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>376</v>
+        <v>345</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>219</v>
+        <v>346</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>220</v>
+        <v>347</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>153</v>
+        <v>348</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6734,13 +6977,13 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>77</v>
+        <v>230</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>77</v>
+        <v>349</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>77</v>
+        <v>350</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6758,31 +7001,31 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>222</v>
+        <v>345</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>176</v>
+        <v>351</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>77</v>
+        <v>351</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>77</v>
+        <v>352</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>77</v>
@@ -6790,18 +7033,18 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>377</v>
+        <v>353</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>306</v>
+        <v>77</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>78</v>
+        <v>354</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>79</v>
@@ -6810,25 +7053,25 @@
         <v>77</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>135</v>
+        <v>355</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>307</v>
+        <v>356</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>308</v>
+        <v>357</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>153</v>
+        <v>358</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>154</v>
+        <v>359</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6865,19 +7108,17 @@
         <v>77</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>309</v>
+        <v>353</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6889,19 +7130,19 @@
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>133</v>
+        <v>361</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>77</v>
+        <v>362</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>77</v>
+        <v>363</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>77</v>
@@ -6909,10 +7150,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6923,7 +7164,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6932,20 +7173,18 @@
         <v>77</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>180</v>
+        <v>104</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>379</v>
+        <v>105</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>381</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6970,13 +7209,13 @@
         <v>77</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>197</v>
+        <v>77</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>382</v>
+        <v>77</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>383</v>
+        <v>77</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>77</v>
@@ -6994,31 +7233,31 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>378</v>
+        <v>107</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>189</v>
+        <v>108</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>189</v>
+        <v>77</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>384</v>
+        <v>77</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>77</v>
@@ -7026,21 +7265,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
@@ -7049,18 +7288,20 @@
         <v>77</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>386</v>
+        <v>111</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>387</v>
+        <v>112</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7109,31 +7350,31 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>385</v>
+        <v>118</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>266</v>
+        <v>108</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>266</v>
+        <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>389</v>
+        <v>77</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>77</v>
@@ -7141,14 +7382,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>390</v>
+        <v>366</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>390</v>
+        <v>366</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>77</v>
+        <v>367</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7161,22 +7402,26 @@
         <v>77</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>391</v>
+        <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>392</v>
+        <v>368</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
       </c>
@@ -7224,7 +7469,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7236,16 +7481,16 @@
         <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>394</v>
+        <v>193</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7256,10 +7501,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>395</v>
+        <v>371</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>395</v>
+        <v>371</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7270,10 +7515,10 @@
         <v>90</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>77</v>
@@ -7282,16 +7527,18 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>295</v>
+        <v>170</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>396</v>
+        <v>372</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>397</v>
+        <v>373</v>
       </c>
       <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
       </c>
@@ -7315,60 +7562,3691 @@
         <v>77</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>77</v>
+        <v>230</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>77</v>
+        <v>375</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>77</v>
+        <v>376</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="P50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO51" t="s" s="2">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="D52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="P52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AO52" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="C53" s="2"/>
+      <c r="D53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO53" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O54" s="2"/>
+      <c r="P54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO54" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AC49" s="2"/>
-      <c r="AD49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE49" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AF49" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AG49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH49" t="s" s="2">
+      <c r="B55" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G55" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AI49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ49" t="s" s="2">
+      <c r="H55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="P55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO55" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AK49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL49" t="s" s="2">
+      <c r="B56" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="N56" s="2"/>
+      <c r="O56" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO56" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AM49" t="s" s="2">
+      <c r="B57" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO57" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AN49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO49" t="s" s="2">
+      <c r="B58" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="D59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O61" s="2"/>
+      <c r="P61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="62" hidden="true">
+      <c r="A62" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="P62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="63" hidden="true">
+      <c r="A63" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="P66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AC80" s="2"/>
+      <c r="AD80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO80" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO49">
+  <autoFilter ref="A1:AO80">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7378,7 +11256,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI48">
+  <conditionalFormatting sqref="A2:AI79">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T10:06:11+00:00</t>
+    <t>2025-02-18T11:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T11:00:40+00:00</t>
+    <t>2025-02-18T15:10:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:10:02+00:00</t>
+    <t>2025-02-18T15:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:17:48+00:00</t>
+    <t>2025-02-18T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:09+00:00</t>
+    <t>2025-02-18T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:38+00:00</t>
+    <t>2025-02-18T15:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:24:54+00:00</t>
+    <t>2025-02-18T15:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:28:32+00:00</t>
+    <t>2025-02-18T15:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:29:38+00:00</t>
+    <t>2025-02-18T15:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:04+00:00</t>
+    <t>2025-02-18T15:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:23+00:00</t>
+    <t>2025-02-18T15:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:53+00:00</t>
+    <t>2025-02-20T13:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:34:17+00:00</t>
+    <t>2025-02-20T13:46:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:46:00+00:00</t>
+    <t>2025-02-20T13:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:48:47+00:00</t>
+    <t>2025-02-20T13:50:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:16+00:00</t>
+    <t>2025-02-20T13:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:51+00:00</t>
+    <t>2025-02-20T13:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:51:52+00:00</t>
+    <t>2025-02-20T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:17+00:00</t>
+    <t>2025-02-20T13:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:53+00:00</t>
+    <t>2025-02-20T14:37:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:37:28+00:00</t>
+    <t>2025-02-20T14:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:00+00:00</t>
+    <t>2025-02-20T14:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:23+00:00</t>
+    <t>2025-02-20T14:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:14+00:00</t>
+    <t>2025-02-20T14:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:55+00:00</t>
+    <t>2025-02-20T14:43:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:43:30+00:00</t>
+    <t>2025-02-20T14:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:45:32+00:00</t>
+    <t>2025-02-20T14:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:47:06+00:00</t>
+    <t>2025-02-20T14:48:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:48:16+00:00</t>
+    <t>2025-02-20T15:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T15:31:18+00:00</t>
+    <t>2025-02-21T13:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T13:12:29+00:00</t>
+    <t>2025-02-21T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3003" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3003" uniqueCount="483">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T15:18:09+00:00</t>
+    <t>2025-02-23T14:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -654,6 +654,10 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}MustBeInteger:La valeur de l'extension versionNumber doit être un entier. {value.matches('^1[0-9]{9}$')}</t>
   </si>
   <si>
     <t>Composition.extension:data-enterer</t>
@@ -4082,7 +4086,7 @@
         <v>204</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>119</v>
+        <v>205</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
@@ -4102,13 +4106,13 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>194</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>77</v>
@@ -4130,13 +4134,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4219,10 +4223,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4248,16 +4252,16 @@
         <v>111</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
@@ -4306,7 +4310,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4338,10 +4342,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4364,16 +4368,16 @@
         <v>91</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4423,7 +4427,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4438,27 +4442,27 @@
         <v>102</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4484,16 +4488,16 @@
         <v>170</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4518,13 +4522,13 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
@@ -4542,7 +4546,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>90</v>
@@ -4557,27 +4561,27 @@
         <v>102</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4600,19 +4604,19 @@
         <v>91</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4640,10 +4644,10 @@
         <v>174</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4661,7 +4665,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>90</v>
@@ -4676,27 +4680,27 @@
         <v>102</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4719,19 +4723,19 @@
         <v>91</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4759,10 +4763,10 @@
         <v>160</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>77</v>
@@ -4780,7 +4784,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4795,27 +4799,27 @@
         <v>102</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>108</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4838,19 +4842,19 @@
         <v>91</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4899,7 +4903,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4917,24 +4921,24 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5046,10 +5050,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5163,10 +5167,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5192,13 +5196,13 @@
         <v>104</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5248,7 +5252,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5257,7 +5261,7 @@
         <v>90</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>102</v>
@@ -5280,10 +5284,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5309,13 +5313,13 @@
         <v>132</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5344,10 +5348,10 @@
         <v>152</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>77</v>
@@ -5365,7 +5369,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5397,10 +5401,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5423,16 +5427,16 @@
         <v>91</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5482,7 +5486,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5500,7 +5504,7 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -5514,10 +5518,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5543,13 +5547,13 @@
         <v>104</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5599,7 +5603,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5631,10 +5635,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5657,17 +5661,17 @@
         <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5716,7 +5720,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5731,27 +5735,27 @@
         <v>102</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5774,19 +5778,19 @@
         <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5835,7 +5839,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>90</v>
@@ -5850,27 +5854,27 @@
         <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5893,17 +5897,17 @@
         <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5952,7 +5956,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>90</v>
@@ -5967,27 +5971,27 @@
         <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6099,10 +6103,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6214,13 +6218,13 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B38" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="B38" t="s" s="2">
-        <v>328</v>
-      </c>
       <c r="C38" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>77</v>
@@ -6242,13 +6246,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6331,10 +6335,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6360,13 +6364,13 @@
         <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6416,7 +6420,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6425,7 +6429,7 @@
         <v>90</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>102</v>
@@ -6448,10 +6452,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6477,13 +6481,13 @@
         <v>132</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6512,10 +6516,10 @@
         <v>152</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>77</v>
@@ -6533,7 +6537,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6565,10 +6569,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6591,16 +6595,16 @@
         <v>91</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6650,7 +6654,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6668,7 +6672,7 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6682,10 +6686,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6711,13 +6715,13 @@
         <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6767,7 +6771,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6799,10 +6803,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6828,13 +6832,13 @@
         <v>104</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6884,7 +6888,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>90</v>
@@ -6902,13 +6906,13 @@
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>77</v>
@@ -6916,10 +6920,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6945,13 +6949,13 @@
         <v>170</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6977,13 +6981,13 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -7001,7 +7005,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7019,13 +7023,13 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>77</v>
@@ -7033,10 +7037,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7044,7 +7048,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>79</v>
@@ -7059,19 +7063,19 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -7108,7 +7112,7 @@
         <v>77</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
@@ -7118,7 +7122,7 @@
         <v>117</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7136,13 +7140,13 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>77</v>
@@ -7150,10 +7154,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7265,10 +7269,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7382,14 +7386,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7411,16 +7415,16 @@
         <v>111</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7469,7 +7473,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7501,10 +7505,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7530,14 +7534,14 @@
         <v>170</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7562,13 +7566,13 @@
         <v>77</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>77</v>
@@ -7586,7 +7590,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>90</v>
@@ -7604,10 +7608,10 @@
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7618,10 +7622,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7644,17 +7648,17 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7703,7 +7707,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7721,10 +7725,10 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7735,10 +7739,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7761,17 +7765,17 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
@@ -7820,7 +7824,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7838,27 +7842,27 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>77</v>
@@ -7880,19 +7884,19 @@
         <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7941,7 +7945,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7959,13 +7963,13 @@
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>77</v>
@@ -7973,10 +7977,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8088,10 +8092,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8205,14 +8209,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8234,16 +8238,16 @@
         <v>111</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8292,7 +8296,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8324,10 +8328,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8353,14 +8357,14 @@
         <v>170</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8370,7 +8374,7 @@
         <v>77</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>77</v>
@@ -8385,13 +8389,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8409,7 +8413,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>90</v>
@@ -8427,10 +8431,10 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8441,10 +8445,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8467,17 +8471,17 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8526,7 +8530,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8544,10 +8548,10 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
@@ -8558,10 +8562,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8584,17 +8588,17 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8643,7 +8647,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8661,27 +8665,27 @@
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>77</v>
@@ -8703,19 +8707,19 @@
         <v>77</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8764,7 +8768,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8782,13 +8786,13 @@
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>77</v>
@@ -8796,10 +8800,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8911,10 +8915,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9028,14 +9032,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9057,16 +9061,16 @@
         <v>111</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -9115,7 +9119,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9147,10 +9151,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9176,14 +9180,14 @@
         <v>170</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9193,7 +9197,7 @@
         <v>77</v>
       </c>
       <c r="S63" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="T63" t="s" s="2">
         <v>77</v>
@@ -9208,13 +9212,13 @@
         <v>77</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>77</v>
@@ -9232,7 +9236,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>90</v>
@@ -9250,10 +9254,10 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -9264,10 +9268,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9290,17 +9294,17 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9349,7 +9353,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9367,10 +9371,10 @@
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>77</v>
@@ -9381,10 +9385,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9407,17 +9411,17 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9466,7 +9470,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9484,24 +9488,24 @@
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9524,19 +9528,19 @@
         <v>91</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -9585,7 +9589,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9603,13 +9607,13 @@
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>77</v>
@@ -9617,10 +9621,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9643,16 +9647,16 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9702,7 +9706,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9720,13 +9724,13 @@
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>77</v>
@@ -9734,10 +9738,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9849,10 +9853,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9966,14 +9970,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -9995,16 +9999,16 @@
         <v>111</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -10053,7 +10057,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10085,10 +10089,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10114,13 +10118,13 @@
         <v>170</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10146,13 +10150,13 @@
         <v>77</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>77</v>
@@ -10170,7 +10174,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>90</v>
@@ -10188,13 +10192,13 @@
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>77</v>
@@ -10202,10 +10206,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10228,13 +10232,13 @@
         <v>77</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10285,7 +10289,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>90</v>
@@ -10303,13 +10307,13 @@
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>77</v>
@@ -10317,10 +10321,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10343,19 +10347,19 @@
         <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -10404,7 +10408,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10422,13 +10426,13 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>77</v>
@@ -10436,10 +10440,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10551,10 +10555,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10668,14 +10672,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10697,16 +10701,16 @@
         <v>111</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>114</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -10755,7 +10759,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10787,10 +10791,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10813,16 +10817,16 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10851,10 +10855,10 @@
         <v>160</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>77</v>
@@ -10872,7 +10876,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10890,13 +10894,13 @@
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>77</v>
@@ -10904,10 +10908,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10930,13 +10934,13 @@
         <v>91</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10987,7 +10991,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11005,13 +11009,13 @@
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>77</v>
@@ -11019,10 +11023,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11045,13 +11049,13 @@
         <v>91</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11102,7 +11106,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11120,7 +11124,7 @@
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>108</v>
@@ -11134,10 +11138,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11160,13 +11164,13 @@
         <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11205,7 +11209,7 @@
         <v>77</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AC80" s="2"/>
       <c r="AD80" t="s" s="2">
@@ -11215,7 +11219,7 @@
         <v>117</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11227,16 +11231,16 @@
         <v>77</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>77</v>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-23T14:02:58+00:00</t>
+    <t>2025-02-24T10:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-Composition-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T10:33:29+00:00</t>
+    <t>2025-02-24T11:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
